--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.83739657867611</v>
+        <v>7.936076944034868</v>
       </c>
       <c r="D2" t="n">
-        <v>47.74177035370052</v>
+        <v>7.758037682476334</v>
       </c>
       <c r="E2" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F2" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.22731556870971</v>
+        <v>9.949438779915328</v>
       </c>
       <c r="D3" t="n">
-        <v>60.48182201752471</v>
+        <v>9.828296077847765</v>
       </c>
       <c r="E3" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F3" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.11530804054617</v>
+        <v>6.518737556588753</v>
       </c>
       <c r="D4" t="n">
-        <v>39.99011350175486</v>
+        <v>6.498393444035164</v>
       </c>
       <c r="E4" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F4" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.18765708847774</v>
+        <v>1.817994276877632</v>
       </c>
       <c r="D5" t="n">
-        <v>10.69517675392967</v>
+        <v>1.737966222513572</v>
       </c>
       <c r="E5" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F5" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.10619305063939</v>
+        <v>2.454756370728901</v>
       </c>
       <c r="D6" t="n">
-        <v>15.04407278353056</v>
+        <v>2.444661827323715</v>
       </c>
       <c r="E6" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F6" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.35278492143617</v>
+        <v>5.907327549733377</v>
       </c>
       <c r="D7" t="n">
-        <v>36.76983743462063</v>
+        <v>5.975098583125853</v>
       </c>
       <c r="E7" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F7" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.00727619272794</v>
+        <v>8.126182381318291</v>
       </c>
       <c r="D8" t="n">
-        <v>50.20919804982651</v>
+        <v>8.158994683096809</v>
       </c>
       <c r="E8" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F8" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.78633532961</v>
+        <v>9.877779491061625</v>
       </c>
       <c r="D9" t="n">
-        <v>61.17872093188944</v>
+        <v>9.941542151432035</v>
       </c>
       <c r="E9" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F9" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.92123049362722</v>
+        <v>6.324699955214424</v>
       </c>
       <c r="D10" t="n">
-        <v>39.74480537871371</v>
+        <v>6.458530874040979</v>
       </c>
       <c r="E10" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F10" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.82354902661619</v>
+        <v>9.071326716825132</v>
       </c>
       <c r="D11" t="n">
-        <v>56.35498702658651</v>
+        <v>9.157685391820308</v>
       </c>
       <c r="E11" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F11" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.34613763503607</v>
+        <v>6.231247365693361</v>
       </c>
       <c r="D12" t="n">
-        <v>39.427085862486</v>
+        <v>6.406901452653974</v>
       </c>
       <c r="E12" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F12" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>61.23661865629149</v>
+        <v>9.950950531647367</v>
       </c>
       <c r="D13" t="n">
-        <v>62.12056098543278</v>
+        <v>10.09459116013283</v>
       </c>
       <c r="E13" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F13" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>55.73093506414596</v>
+        <v>9.056276947923719</v>
       </c>
       <c r="D14" t="n">
-        <v>56.69050631696625</v>
+        <v>9.212207276507016</v>
       </c>
       <c r="E14" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F14" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>63.50010187622373</v>
+        <v>10.31876655488636</v>
       </c>
       <c r="D15" t="n">
-        <v>64.56416729791748</v>
+        <v>10.49167718591159</v>
       </c>
       <c r="E15" t="n">
-        <v>16.04371102209304</v>
+        <v>2.607103041090119</v>
       </c>
       <c r="F15" t="n">
-        <v>16.24497554022708</v>
+        <v>2.639808525286901</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
